--- a/tools/importer/reports/import-wknd-adventure.report.xlsx
+++ b/tools/importer/reports/import-wknd-adventure.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="188">
   <si>
     <t>_reportFile</t>
   </si>
@@ -19,6 +19,12 @@
     <t>blocks</t>
   </si>
   <si>
+    <t>error</t>
+  </si>
+  <si>
+    <t>errorStack</t>
+  </si>
+  <si>
     <t>path</t>
   </si>
   <si>
@@ -43,6 +49,9 @@
     <t>["cards-team","cards-team"]</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>about-us</t>
   </si>
   <si>
@@ -52,7 +61,7 @@
     <t>wknd-about-us</t>
   </si>
   <si>
-    <t>2026-08-07T05:52:49.618Z</t>
+    <t>2026-08-07T09:09:17.016Z</t>
   </si>
   <si>
     <t>About Us</t>
@@ -136,7 +145,7 @@
     <t>wknd-faqs</t>
   </si>
   <si>
-    <t>2026-08-07T07:29:43.249Z</t>
+    <t>2026-08-07T09:09:22.340Z</t>
   </si>
   <si>
     <t>FAQs</t>
@@ -148,9 +157,6 @@
     <t>footer.report.json</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>footer</t>
   </si>
   <si>
@@ -220,7 +226,7 @@
     <t>wknd-adventure</t>
   </si>
   <si>
-    <t>2026-08-07T07:38:30.153Z</t>
+    <t>2026-08-10T09:12:36.977Z</t>
   </si>
   <si>
     <t>Bali Surf Camp</t>
@@ -235,7 +241,7 @@
     <t>adventures/beervana-portland</t>
   </si>
   <si>
-    <t>2026-08-07T07:38:35.102Z</t>
+    <t>2026-08-10T09:12:42.492Z</t>
   </si>
   <si>
     <t>Beervana in Portland</t>
@@ -250,7 +256,7 @@
     <t>adventures/climbing-new-zealand</t>
   </si>
   <si>
-    <t>2026-08-07T07:38:40.420Z</t>
+    <t>2026-08-10T09:12:47.536Z</t>
   </si>
   <si>
     <t>Climbing New Zealand</t>
@@ -265,7 +271,7 @@
     <t>adventures/colorado-rock-climbing</t>
   </si>
   <si>
-    <t>2026-08-07T07:38:44.575Z</t>
+    <t>2026-08-10T09:12:51.409Z</t>
   </si>
   <si>
     <t>Colorado Rock Climbing</t>
@@ -280,7 +286,7 @@
     <t>adventures/cycling-southern-utah</t>
   </si>
   <si>
-    <t>2026-08-07T07:38:49.597Z</t>
+    <t>2026-08-10T09:12:56.494Z</t>
   </si>
   <si>
     <t>Cycling Southern Utah</t>
@@ -295,7 +301,7 @@
     <t>adventures/cycling-tuscany</t>
   </si>
   <si>
-    <t>2026-08-07T08:44:55.410Z</t>
+    <t>2026-08-10T09:13:02.557Z</t>
   </si>
   <si>
     <t>Cycling Tuscany</t>
@@ -310,7 +316,7 @@
     <t>adventures/downhill-skiing-wyoming</t>
   </si>
   <si>
-    <t>2026-08-07T08:45:01.304Z</t>
+    <t>2026-08-10T09:13:08.173Z</t>
   </si>
   <si>
     <t>Downhill Skiing Wyoming</t>
@@ -325,7 +331,7 @@
     <t>adventures/gastronomic-marais-tour</t>
   </si>
   <si>
-    <t>2026-08-07T08:45:06.177Z</t>
+    <t>2026-08-10T09:13:14.040Z</t>
   </si>
   <si>
     <t>Gastronomic Marais Tour</t>
@@ -340,7 +346,7 @@
     <t>adventures/napa-wine-tasting</t>
   </si>
   <si>
-    <t>2026-08-07T08:45:11.254Z</t>
+    <t>2026-08-10T09:13:17.708Z</t>
   </si>
   <si>
     <t>Napa Wine Tasting</t>
@@ -355,7 +361,7 @@
     <t>adventures/riverside-camping-australia</t>
   </si>
   <si>
-    <t>2026-08-07T08:45:15.620Z</t>
+    <t>2026-08-10T09:13:21.775Z</t>
   </si>
   <si>
     <t>Riverside Camping</t>
@@ -370,7 +376,7 @@
     <t>adventures/ski-touring-mont-blanc</t>
   </si>
   <si>
-    <t>2026-08-07T08:45:21.116Z</t>
+    <t>2026-08-10T09:13:26.308Z</t>
   </si>
   <si>
     <t>Ski Touring Mont Blanc</t>
@@ -385,7 +391,7 @@
     <t>adventures/surf-camp-costa-rica</t>
   </si>
   <si>
-    <t>2026-08-07T08:45:26.472Z</t>
+    <t>2026-08-10T09:13:32.129Z</t>
   </si>
   <si>
     <t>Surf Camp in Costa Rica</t>
@@ -400,7 +406,7 @@
     <t>adventures/tahoe-skiing</t>
   </si>
   <si>
-    <t>2026-08-07T08:45:31.906Z</t>
+    <t>2026-08-10T09:13:37.130Z</t>
   </si>
   <si>
     <t>Tahoe Skiing</t>
@@ -415,7 +421,7 @@
     <t>adventures/west-coast-cycling</t>
   </si>
   <si>
-    <t>2026-08-07T08:45:37.465Z</t>
+    <t>2026-08-10T09:13:42.835Z</t>
   </si>
   <si>
     <t>West Coast Cycling</t>
@@ -430,7 +436,7 @@
     <t>adventures/whistler-mountain-biking</t>
   </si>
   <si>
-    <t>2026-08-07T08:45:43.291Z</t>
+    <t>2026-08-10T09:13:49.554Z</t>
   </si>
   <si>
     <t>Whistler Mountain Biking</t>
@@ -445,7 +451,7 @@
     <t>adventures/yosemite-backpacking</t>
   </si>
   <si>
-    <t>2026-08-07T08:45:48.684Z</t>
+    <t>2026-08-10T09:13:53.956Z</t>
   </si>
   <si>
     <t>Yosemite Backpacking</t>
@@ -490,7 +496,7 @@
     <t>magazine/arctic-surfing</t>
   </si>
   <si>
-    <t>2026-08-07T07:23:48.672Z</t>
+    <t>2026-08-07T09:09:26.685Z</t>
   </si>
   <si>
     <t>magazine/guide-la-skateparks.report.json</t>
@@ -499,7 +505,7 @@
     <t>magazine/guide-la-skateparks</t>
   </si>
   <si>
-    <t>2026-08-07T07:23:52.813Z</t>
+    <t>2026-08-07T09:09:31.643Z</t>
   </si>
   <si>
     <t>Ultimate Guide to LA Skateparks</t>
@@ -514,7 +520,7 @@
     <t>magazine/san-diego-surf</t>
   </si>
   <si>
-    <t>2026-08-07T07:23:57.737Z</t>
+    <t>2026-08-07T09:09:35.685Z</t>
   </si>
   <si>
     <t>San Diego Surf Spots</t>
@@ -529,7 +535,7 @@
     <t>magazine/ski-touring</t>
   </si>
   <si>
-    <t>2026-08-07T07:24:03.356Z</t>
+    <t>2026-08-07T09:09:39.945Z</t>
   </si>
   <si>
     <t>Ski Touring</t>
@@ -544,13 +550,33 @@
     <t>magazine/western-australia</t>
   </si>
   <si>
-    <t>2026-08-07T07:24:07.536Z</t>
+    <t>2026-08-07T09:09:44.331Z</t>
   </si>
   <si>
     <t>Western Australia</t>
   </si>
   <si>
     <t>https://wknd.site/us/en/magazine/western-australia.html</t>
+  </si>
+  <si>
+    <t>us/en/adventures/yosemite-backpacking.html.report.json</t>
+  </si>
+  <si>
+    <t>page.evaluate: Target page, context or browser has been closed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">page.evaluate: Target page, context or browser has been closed
+    at processUrl (/home/node/.excat-marketplaces/excat-marketplace/excat/skills/excat-content-import/scripts/run-bulk-import.js:479:16)
+    at async main (/home/node/.excat-marketplaces/excat-marketplace/excat/skills/excat-content-import/scripts/run-bulk-import.js:696:22)</t>
+  </si>
+  <si>
+    <t>us/en/adventures/yosemite-backpacking.html</t>
+  </si>
+  <si>
+    <t>failed</t>
+  </si>
+  <si>
+    <t>2026-08-10T09:12:25.649Z</t>
   </si>
 </sst>
 </file>
@@ -939,17 +965,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="5" max="5" width="17" customWidth="1"/>
-    <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="8" width="50" customWidth="1"/>
+    <col min="1" max="4" width="50" customWidth="1"/>
+    <col min="5" max="5" width="44" customWidth="1"/>
+    <col min="7" max="7" width="17" customWidth="1"/>
+    <col min="8" max="8" width="26" customWidth="1"/>
+    <col min="9" max="10" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -974,155 +1000,191 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="I3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F4" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+      <c r="I4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F5" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="G5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+      <c r="I5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="G6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+      <c r="I6" t="s">
+        <v>45</v>
+      </c>
+      <c r="J6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F7" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="G7" t="s">
         <v>49</v>
@@ -1130,103 +1192,127 @@
       <c r="H7" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I7" t="s">
+        <v>51</v>
+      </c>
+      <c r="J7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C8" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="G8" t="s">
         <v>56</v>
       </c>
       <c r="H8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+      <c r="I8" t="s">
+        <v>58</v>
+      </c>
+      <c r="J8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="F9" t="s">
-        <v>59</v>
+        <v>14</v>
       </c>
       <c r="G9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+      <c r="I9" t="s">
+        <v>38</v>
+      </c>
+      <c r="J9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>61</v>
+        <v>12</v>
       </c>
       <c r="D10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F10" t="s">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="G10" t="s">
         <v>64</v>
       </c>
       <c r="H10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+      <c r="I10" t="s">
+        <v>66</v>
+      </c>
+      <c r="J10" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C11" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="D11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F11" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="G11" t="s">
         <v>70</v>
@@ -1234,415 +1320,511 @@
       <c r="H11" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I11" t="s">
+        <v>72</v>
+      </c>
+      <c r="J11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C12" t="s">
-        <v>73</v>
+        <v>12</v>
       </c>
       <c r="D12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="F12" t="s">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="G12" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="H12" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I12" t="s">
+        <v>77</v>
+      </c>
+      <c r="J12" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B13" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C13" t="s">
-        <v>78</v>
+        <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="F13" t="s">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="G13" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="H13" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I13" t="s">
+        <v>82</v>
+      </c>
+      <c r="J13" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
       <c r="D14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="F14" t="s">
-        <v>84</v>
+        <v>14</v>
       </c>
       <c r="G14" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="H14" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I14" t="s">
+        <v>87</v>
+      </c>
+      <c r="J14" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>88</v>
+        <v>12</v>
       </c>
       <c r="D15" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="F15" t="s">
-        <v>89</v>
+        <v>14</v>
       </c>
       <c r="G15" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="H15" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I15" t="s">
+        <v>92</v>
+      </c>
+      <c r="J15" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B16" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>93</v>
+        <v>12</v>
       </c>
       <c r="D16" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E16" t="s">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="F16" t="s">
-        <v>94</v>
+        <v>14</v>
       </c>
       <c r="G16" t="s">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="H16" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I16" t="s">
+        <v>97</v>
+      </c>
+      <c r="J16" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B17" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C17" t="s">
-        <v>98</v>
+        <v>12</v>
       </c>
       <c r="D17" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E17" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="F17" t="s">
-        <v>99</v>
+        <v>14</v>
       </c>
       <c r="G17" t="s">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="H17" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I17" t="s">
+        <v>102</v>
+      </c>
+      <c r="J17" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B18" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C18" t="s">
-        <v>103</v>
+        <v>12</v>
       </c>
       <c r="D18" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E18" t="s">
-        <v>68</v>
+        <v>105</v>
       </c>
       <c r="F18" t="s">
-        <v>104</v>
+        <v>14</v>
       </c>
       <c r="G18" t="s">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="H18" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I18" t="s">
+        <v>107</v>
+      </c>
+      <c r="J18" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B19" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C19" t="s">
-        <v>108</v>
+        <v>12</v>
       </c>
       <c r="D19" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E19" t="s">
-        <v>68</v>
+        <v>110</v>
       </c>
       <c r="F19" t="s">
-        <v>109</v>
+        <v>14</v>
       </c>
       <c r="G19" t="s">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="H19" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I19" t="s">
+        <v>112</v>
+      </c>
+      <c r="J19" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B20" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C20" t="s">
-        <v>113</v>
+        <v>12</v>
       </c>
       <c r="D20" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E20" t="s">
-        <v>68</v>
+        <v>115</v>
       </c>
       <c r="F20" t="s">
-        <v>114</v>
+        <v>14</v>
       </c>
       <c r="G20" t="s">
-        <v>115</v>
+        <v>70</v>
       </c>
       <c r="H20" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I20" t="s">
+        <v>117</v>
+      </c>
+      <c r="J20" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B21" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C21" t="s">
-        <v>118</v>
+        <v>12</v>
       </c>
       <c r="D21" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E21" t="s">
-        <v>68</v>
+        <v>120</v>
       </c>
       <c r="F21" t="s">
-        <v>119</v>
+        <v>14</v>
       </c>
       <c r="G21" t="s">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="H21" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I21" t="s">
+        <v>122</v>
+      </c>
+      <c r="J21" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B22" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C22" t="s">
-        <v>123</v>
+        <v>12</v>
       </c>
       <c r="D22" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E22" t="s">
-        <v>68</v>
+        <v>125</v>
       </c>
       <c r="F22" t="s">
-        <v>124</v>
+        <v>14</v>
       </c>
       <c r="G22" t="s">
-        <v>125</v>
+        <v>70</v>
       </c>
       <c r="H22" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I22" t="s">
+        <v>127</v>
+      </c>
+      <c r="J22" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B23" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C23" t="s">
-        <v>128</v>
+        <v>12</v>
       </c>
       <c r="D23" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E23" t="s">
-        <v>68</v>
+        <v>130</v>
       </c>
       <c r="F23" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="G23" t="s">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="H23" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I23" t="s">
+        <v>132</v>
+      </c>
+      <c r="J23" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B24" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C24" t="s">
-        <v>133</v>
+        <v>12</v>
       </c>
       <c r="D24" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E24" t="s">
-        <v>68</v>
+        <v>135</v>
       </c>
       <c r="F24" t="s">
-        <v>134</v>
+        <v>14</v>
       </c>
       <c r="G24" t="s">
-        <v>135</v>
+        <v>70</v>
       </c>
       <c r="H24" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I24" t="s">
+        <v>137</v>
+      </c>
+      <c r="J24" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B25" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C25" t="s">
-        <v>138</v>
+        <v>12</v>
       </c>
       <c r="D25" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E25" t="s">
-        <v>68</v>
+        <v>140</v>
       </c>
       <c r="F25" t="s">
-        <v>139</v>
+        <v>14</v>
       </c>
       <c r="G25" t="s">
-        <v>140</v>
+        <v>70</v>
       </c>
       <c r="H25" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I25" t="s">
+        <v>142</v>
+      </c>
+      <c r="J25" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B26" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C26" t="s">
-        <v>143</v>
+        <v>12</v>
       </c>
       <c r="D26" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E26" t="s">
-        <v>68</v>
+        <v>145</v>
       </c>
       <c r="F26" t="s">
-        <v>144</v>
+        <v>14</v>
       </c>
       <c r="G26" t="s">
-        <v>145</v>
+        <v>70</v>
       </c>
       <c r="H26" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I26" t="s">
+        <v>147</v>
+      </c>
+      <c r="J26" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B27" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C27" t="s">
-        <v>149</v>
+        <v>12</v>
       </c>
       <c r="D27" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E27" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F27" t="s">
-        <v>151</v>
+        <v>14</v>
       </c>
       <c r="G27" t="s">
         <v>152</v>
@@ -1650,165 +1832,239 @@
       <c r="H27" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I27" t="s">
+        <v>154</v>
+      </c>
+      <c r="J27" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B28" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C28" t="s">
-        <v>155</v>
+        <v>12</v>
       </c>
       <c r="D28" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E28" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="F28" t="s">
-        <v>156</v>
+        <v>14</v>
       </c>
       <c r="G28" t="s">
         <v>152</v>
       </c>
       <c r="H28" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+        <v>158</v>
+      </c>
+      <c r="I28" t="s">
+        <v>154</v>
+      </c>
+      <c r="J28" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B29" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C29" t="s">
-        <v>158</v>
+        <v>12</v>
       </c>
       <c r="D29" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E29" t="s">
-        <v>26</v>
+        <v>160</v>
       </c>
       <c r="F29" t="s">
-        <v>159</v>
+        <v>14</v>
       </c>
       <c r="G29" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H29" t="s">
+        <v>161</v>
+      </c>
+      <c r="I29" t="s">
+        <v>31</v>
+      </c>
+      <c r="J29" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>162</v>
+      </c>
+      <c r="B30" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" t="s">
+        <v>12</v>
+      </c>
+      <c r="D30" t="s">
+        <v>12</v>
+      </c>
+      <c r="E30" t="s">
+        <v>163</v>
+      </c>
+      <c r="F30" t="s">
+        <v>14</v>
+      </c>
+      <c r="G30" t="s">
         <v>29</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>160</v>
-      </c>
-      <c r="B30" t="s">
-        <v>24</v>
-      </c>
-      <c r="C30" t="s">
-        <v>161</v>
-      </c>
-      <c r="D30" t="s">
-        <v>11</v>
-      </c>
-      <c r="E30" t="s">
-        <v>26</v>
-      </c>
-      <c r="F30" t="s">
-        <v>162</v>
-      </c>
-      <c r="G30" t="s">
-        <v>163</v>
       </c>
       <c r="H30" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I30" t="s">
+        <v>165</v>
+      </c>
+      <c r="J30" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B31" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C31" t="s">
-        <v>166</v>
+        <v>12</v>
       </c>
       <c r="D31" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E31" t="s">
-        <v>26</v>
+        <v>168</v>
       </c>
       <c r="F31" t="s">
-        <v>167</v>
+        <v>14</v>
       </c>
       <c r="G31" t="s">
-        <v>168</v>
+        <v>29</v>
       </c>
       <c r="H31" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I31" t="s">
+        <v>170</v>
+      </c>
+      <c r="J31" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B32" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C32" t="s">
-        <v>171</v>
+        <v>12</v>
       </c>
       <c r="D32" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E32" t="s">
-        <v>26</v>
+        <v>173</v>
       </c>
       <c r="F32" t="s">
-        <v>172</v>
+        <v>14</v>
       </c>
       <c r="G32" t="s">
-        <v>173</v>
+        <v>29</v>
       </c>
       <c r="H32" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I32" t="s">
+        <v>175</v>
+      </c>
+      <c r="J32" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B33" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C33" t="s">
-        <v>176</v>
+        <v>12</v>
       </c>
       <c r="D33" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E33" t="s">
-        <v>26</v>
+        <v>178</v>
       </c>
       <c r="F33" t="s">
-        <v>177</v>
+        <v>14</v>
       </c>
       <c r="G33" t="s">
-        <v>178</v>
+        <v>29</v>
       </c>
       <c r="H33" t="s">
         <v>179</v>
       </c>
+      <c r="I33" t="s">
+        <v>180</v>
+      </c>
+      <c r="J33" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>182</v>
+      </c>
+      <c r="B34" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" t="s">
+        <v>183</v>
+      </c>
+      <c r="D34" t="s">
+        <v>184</v>
+      </c>
+      <c r="E34" t="s">
+        <v>185</v>
+      </c>
+      <c r="F34" t="s">
+        <v>186</v>
+      </c>
+      <c r="G34" t="s">
+        <v>12</v>
+      </c>
+      <c r="H34" t="s">
+        <v>187</v>
+      </c>
+      <c r="I34" t="s">
+        <v>12</v>
+      </c>
+      <c r="J34" t="s">
+        <v>148</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1"/>
+  <autoFilter ref="A1:J1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/tools/importer/reports/import-wknd-adventure.report.xlsx
+++ b/tools/importer/reports/import-wknd-adventure.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="193">
   <si>
     <t>_reportFile</t>
   </si>
@@ -163,7 +163,7 @@
     <t>wknd-footer</t>
   </si>
   <si>
-    <t>2026-08-07T07:19:13.030Z</t>
+    <t>2026-08-10T10:18:15.420Z</t>
   </si>
   <si>
     <t>Footer</t>
@@ -208,16 +208,31 @@
     <t>wknd-nav</t>
   </si>
   <si>
-    <t>2026-08-07T07:19:09.359Z</t>
+    <t>2026-08-10T10:18:20.500Z</t>
   </si>
   <si>
     <t>Nav</t>
   </si>
   <si>
+    <t>search.report.json</t>
+  </si>
+  <si>
+    <t>search</t>
+  </si>
+  <si>
+    <t>wknd-search</t>
+  </si>
+  <si>
+    <t>2026-08-10T10:19:05.005Z</t>
+  </si>
+  <si>
+    <t>Search</t>
+  </si>
+  <si>
     <t>adventures/bali-surf-camp.report.json</t>
   </si>
   <si>
-    <t>["trip-details"]</t>
+    <t>["trip-details","tabs"]</t>
   </si>
   <si>
     <t>adventures/bali-surf-camp</t>
@@ -226,7 +241,7 @@
     <t>wknd-adventure</t>
   </si>
   <si>
-    <t>2026-08-10T09:12:36.977Z</t>
+    <t>2026-08-11T05:38:36.943Z</t>
   </si>
   <si>
     <t>Bali Surf Camp</t>
@@ -241,7 +256,7 @@
     <t>adventures/beervana-portland</t>
   </si>
   <si>
-    <t>2026-08-10T09:12:42.492Z</t>
+    <t>2026-08-11T05:38:43.191Z</t>
   </si>
   <si>
     <t>Beervana in Portland</t>
@@ -256,7 +271,7 @@
     <t>adventures/climbing-new-zealand</t>
   </si>
   <si>
-    <t>2026-08-10T09:12:47.536Z</t>
+    <t>2026-08-11T05:38:49.328Z</t>
   </si>
   <si>
     <t>Climbing New Zealand</t>
@@ -271,7 +286,7 @@
     <t>adventures/colorado-rock-climbing</t>
   </si>
   <si>
-    <t>2026-08-10T09:12:51.409Z</t>
+    <t>2026-08-11T05:38:55.058Z</t>
   </si>
   <si>
     <t>Colorado Rock Climbing</t>
@@ -286,7 +301,7 @@
     <t>adventures/cycling-southern-utah</t>
   </si>
   <si>
-    <t>2026-08-10T09:12:56.494Z</t>
+    <t>2026-08-11T05:39:00.011Z</t>
   </si>
   <si>
     <t>Cycling Southern Utah</t>
@@ -301,7 +316,7 @@
     <t>adventures/cycling-tuscany</t>
   </si>
   <si>
-    <t>2026-08-10T09:13:02.557Z</t>
+    <t>2026-08-11T05:39:05.111Z</t>
   </si>
   <si>
     <t>Cycling Tuscany</t>
@@ -316,7 +331,7 @@
     <t>adventures/downhill-skiing-wyoming</t>
   </si>
   <si>
-    <t>2026-08-10T09:13:08.173Z</t>
+    <t>2026-08-11T05:39:11.402Z</t>
   </si>
   <si>
     <t>Downhill Skiing Wyoming</t>
@@ -331,7 +346,7 @@
     <t>adventures/gastronomic-marais-tour</t>
   </si>
   <si>
-    <t>2026-08-10T09:13:14.040Z</t>
+    <t>2026-08-11T05:39:15.940Z</t>
   </si>
   <si>
     <t>Gastronomic Marais Tour</t>
@@ -346,7 +361,7 @@
     <t>adventures/napa-wine-tasting</t>
   </si>
   <si>
-    <t>2026-08-10T09:13:17.708Z</t>
+    <t>2026-08-11T05:39:21.279Z</t>
   </si>
   <si>
     <t>Napa Wine Tasting</t>
@@ -361,7 +376,7 @@
     <t>adventures/riverside-camping-australia</t>
   </si>
   <si>
-    <t>2026-08-10T09:13:21.775Z</t>
+    <t>2026-08-11T05:39:26.898Z</t>
   </si>
   <si>
     <t>Riverside Camping</t>
@@ -376,7 +391,7 @@
     <t>adventures/ski-touring-mont-blanc</t>
   </si>
   <si>
-    <t>2026-08-10T09:13:26.308Z</t>
+    <t>2026-08-11T05:39:32.274Z</t>
   </si>
   <si>
     <t>Ski Touring Mont Blanc</t>
@@ -391,7 +406,7 @@
     <t>adventures/surf-camp-costa-rica</t>
   </si>
   <si>
-    <t>2026-08-10T09:13:32.129Z</t>
+    <t>2026-08-11T05:39:37.156Z</t>
   </si>
   <si>
     <t>Surf Camp in Costa Rica</t>
@@ -406,7 +421,7 @@
     <t>adventures/tahoe-skiing</t>
   </si>
   <si>
-    <t>2026-08-10T09:13:37.130Z</t>
+    <t>2026-08-11T05:39:43.313Z</t>
   </si>
   <si>
     <t>Tahoe Skiing</t>
@@ -421,7 +436,7 @@
     <t>adventures/west-coast-cycling</t>
   </si>
   <si>
-    <t>2026-08-10T09:13:42.835Z</t>
+    <t>2026-08-11T05:39:47.535Z</t>
   </si>
   <si>
     <t>West Coast Cycling</t>
@@ -436,7 +451,7 @@
     <t>adventures/whistler-mountain-biking</t>
   </si>
   <si>
-    <t>2026-08-10T09:13:49.554Z</t>
+    <t>2026-08-11T05:39:54.118Z</t>
   </si>
   <si>
     <t>Whistler Mountain Biking</t>
@@ -451,7 +466,7 @@
     <t>adventures/yosemite-backpacking</t>
   </si>
   <si>
-    <t>2026-08-10T09:13:53.956Z</t>
+    <t>2026-08-11T05:39:59.135Z</t>
   </si>
   <si>
     <t>Yosemite Backpacking</t>
@@ -965,7 +980,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="4" width="50" customWidth="1"/>
@@ -1300,54 +1315,54 @@
         <v>67</v>
       </c>
       <c r="B11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" t="s">
         <v>68</v>
       </c>
-      <c r="C11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" t="s">
         <v>69</v>
       </c>
-      <c r="F11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>70</v>
       </c>
-      <c r="H11" t="s">
+      <c r="I11" t="s">
         <v>71</v>
       </c>
-      <c r="I11" t="s">
-        <v>72</v>
-      </c>
       <c r="J11" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>72</v>
+      </c>
+      <c r="B12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" t="s">
         <v>74</v>
       </c>
-      <c r="B12" t="s">
-        <v>68</v>
-      </c>
-      <c r="C12" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" t="s">
         <v>75</v>
-      </c>
-      <c r="F12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G12" t="s">
-        <v>70</v>
       </c>
       <c r="H12" t="s">
         <v>76</v>
@@ -1364,7 +1379,7 @@
         <v>79</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
         <v>12</v>
@@ -1379,7 +1394,7 @@
         <v>14</v>
       </c>
       <c r="G13" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H13" t="s">
         <v>81</v>
@@ -1396,7 +1411,7 @@
         <v>84</v>
       </c>
       <c r="B14" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
         <v>12</v>
@@ -1411,7 +1426,7 @@
         <v>14</v>
       </c>
       <c r="G14" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H14" t="s">
         <v>86</v>
@@ -1428,7 +1443,7 @@
         <v>89</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C15" t="s">
         <v>12</v>
@@ -1443,7 +1458,7 @@
         <v>14</v>
       </c>
       <c r="G15" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H15" t="s">
         <v>91</v>
@@ -1460,7 +1475,7 @@
         <v>94</v>
       </c>
       <c r="B16" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C16" t="s">
         <v>12</v>
@@ -1475,7 +1490,7 @@
         <v>14</v>
       </c>
       <c r="G16" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H16" t="s">
         <v>96</v>
@@ -1492,7 +1507,7 @@
         <v>99</v>
       </c>
       <c r="B17" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C17" t="s">
         <v>12</v>
@@ -1507,7 +1522,7 @@
         <v>14</v>
       </c>
       <c r="G17" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H17" t="s">
         <v>101</v>
@@ -1524,7 +1539,7 @@
         <v>104</v>
       </c>
       <c r="B18" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C18" t="s">
         <v>12</v>
@@ -1539,7 +1554,7 @@
         <v>14</v>
       </c>
       <c r="G18" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H18" t="s">
         <v>106</v>
@@ -1556,7 +1571,7 @@
         <v>109</v>
       </c>
       <c r="B19" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C19" t="s">
         <v>12</v>
@@ -1571,7 +1586,7 @@
         <v>14</v>
       </c>
       <c r="G19" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H19" t="s">
         <v>111</v>
@@ -1588,7 +1603,7 @@
         <v>114</v>
       </c>
       <c r="B20" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C20" t="s">
         <v>12</v>
@@ -1603,7 +1618,7 @@
         <v>14</v>
       </c>
       <c r="G20" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H20" t="s">
         <v>116</v>
@@ -1620,7 +1635,7 @@
         <v>119</v>
       </c>
       <c r="B21" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C21" t="s">
         <v>12</v>
@@ -1635,7 +1650,7 @@
         <v>14</v>
       </c>
       <c r="G21" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H21" t="s">
         <v>121</v>
@@ -1652,7 +1667,7 @@
         <v>124</v>
       </c>
       <c r="B22" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C22" t="s">
         <v>12</v>
@@ -1667,7 +1682,7 @@
         <v>14</v>
       </c>
       <c r="G22" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H22" t="s">
         <v>126</v>
@@ -1684,7 +1699,7 @@
         <v>129</v>
       </c>
       <c r="B23" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C23" t="s">
         <v>12</v>
@@ -1699,7 +1714,7 @@
         <v>14</v>
       </c>
       <c r="G23" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H23" t="s">
         <v>131</v>
@@ -1716,7 +1731,7 @@
         <v>134</v>
       </c>
       <c r="B24" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C24" t="s">
         <v>12</v>
@@ -1731,7 +1746,7 @@
         <v>14</v>
       </c>
       <c r="G24" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H24" t="s">
         <v>136</v>
@@ -1748,7 +1763,7 @@
         <v>139</v>
       </c>
       <c r="B25" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C25" t="s">
         <v>12</v>
@@ -1763,7 +1778,7 @@
         <v>14</v>
       </c>
       <c r="G25" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H25" t="s">
         <v>141</v>
@@ -1780,7 +1795,7 @@
         <v>144</v>
       </c>
       <c r="B26" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C26" t="s">
         <v>12</v>
@@ -1795,7 +1810,7 @@
         <v>14</v>
       </c>
       <c r="G26" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H26" t="s">
         <v>146</v>
@@ -1812,100 +1827,100 @@
         <v>149</v>
       </c>
       <c r="B27" t="s">
+        <v>73</v>
+      </c>
+      <c r="C27" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" t="s">
+        <v>12</v>
+      </c>
+      <c r="E27" t="s">
         <v>150</v>
       </c>
-      <c r="C27" t="s">
-        <v>12</v>
-      </c>
-      <c r="D27" t="s">
-        <v>12</v>
-      </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27" t="s">
+        <v>75</v>
+      </c>
+      <c r="H27" t="s">
         <v>151</v>
       </c>
-      <c r="F27" t="s">
-        <v>14</v>
-      </c>
-      <c r="G27" t="s">
+      <c r="I27" t="s">
         <v>152</v>
       </c>
-      <c r="H27" t="s">
+      <c r="J27" t="s">
         <v>153</v>
-      </c>
-      <c r="I27" t="s">
-        <v>154</v>
-      </c>
-      <c r="J27" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>154</v>
+      </c>
+      <c r="B28" t="s">
+        <v>155</v>
+      </c>
+      <c r="C28" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" t="s">
+        <v>12</v>
+      </c>
+      <c r="E28" t="s">
         <v>156</v>
       </c>
-      <c r="B28" t="s">
-        <v>150</v>
-      </c>
-      <c r="C28" t="s">
-        <v>12</v>
-      </c>
-      <c r="D28" t="s">
-        <v>12</v>
-      </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
+        <v>14</v>
+      </c>
+      <c r="G28" t="s">
         <v>157</v>
-      </c>
-      <c r="F28" t="s">
-        <v>14</v>
-      </c>
-      <c r="G28" t="s">
-        <v>152</v>
       </c>
       <c r="H28" t="s">
         <v>158</v>
       </c>
       <c r="I28" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="J28" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>161</v>
+      </c>
+      <c r="B29" t="s">
+        <v>155</v>
+      </c>
+      <c r="C29" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" t="s">
+        <v>12</v>
+      </c>
+      <c r="E29" t="s">
+        <v>162</v>
+      </c>
+      <c r="F29" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29" t="s">
+        <v>157</v>
+      </c>
+      <c r="H29" t="s">
+        <v>163</v>
+      </c>
+      <c r="I29" t="s">
         <v>159</v>
       </c>
-      <c r="B29" t="s">
-        <v>27</v>
-      </c>
-      <c r="C29" t="s">
-        <v>12</v>
-      </c>
-      <c r="D29" t="s">
-        <v>12</v>
-      </c>
-      <c r="E29" t="s">
+      <c r="J29" t="s">
         <v>160</v>
-      </c>
-      <c r="F29" t="s">
-        <v>14</v>
-      </c>
-      <c r="G29" t="s">
-        <v>29</v>
-      </c>
-      <c r="H29" t="s">
-        <v>161</v>
-      </c>
-      <c r="I29" t="s">
-        <v>31</v>
-      </c>
-      <c r="J29" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B30" t="s">
         <v>27</v>
@@ -1917,7 +1932,7 @@
         <v>12</v>
       </c>
       <c r="E30" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F30" t="s">
         <v>14</v>
@@ -1926,13 +1941,13 @@
         <v>29</v>
       </c>
       <c r="H30" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="I30" t="s">
-        <v>165</v>
+        <v>31</v>
       </c>
       <c r="J30" t="s">
-        <v>166</v>
+        <v>32</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -2036,31 +2051,63 @@
         <v>182</v>
       </c>
       <c r="B34" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="C34" t="s">
+        <v>12</v>
+      </c>
+      <c r="D34" t="s">
+        <v>12</v>
+      </c>
+      <c r="E34" t="s">
         <v>183</v>
       </c>
-      <c r="D34" t="s">
+      <c r="F34" t="s">
+        <v>14</v>
+      </c>
+      <c r="G34" t="s">
+        <v>29</v>
+      </c>
+      <c r="H34" t="s">
         <v>184</v>
       </c>
-      <c r="E34" t="s">
+      <c r="I34" t="s">
         <v>185</v>
       </c>
-      <c r="F34" t="s">
+      <c r="J34" t="s">
         <v>186</v>
       </c>
-      <c r="G34" t="s">
-        <v>12</v>
-      </c>
-      <c r="H34" t="s">
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>187</v>
       </c>
-      <c r="I34" t="s">
-        <v>12</v>
-      </c>
-      <c r="J34" t="s">
-        <v>148</v>
+      <c r="B35" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35" t="s">
+        <v>188</v>
+      </c>
+      <c r="D35" t="s">
+        <v>189</v>
+      </c>
+      <c r="E35" t="s">
+        <v>190</v>
+      </c>
+      <c r="F35" t="s">
+        <v>191</v>
+      </c>
+      <c r="G35" t="s">
+        <v>12</v>
+      </c>
+      <c r="H35" t="s">
+        <v>192</v>
+      </c>
+      <c r="I35" t="s">
+        <v>12</v>
+      </c>
+      <c r="J35" t="s">
+        <v>153</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-wknd-adventure.report.xlsx
+++ b/tools/importer/reports/import-wknd-adventure.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="274">
   <si>
     <t>_reportFile</t>
   </si>
@@ -61,7 +61,7 @@
     <t>wknd-about-us</t>
   </si>
   <si>
-    <t>2026-08-07T09:09:17.016Z</t>
+    <t>2026-08-11T06:03:14.902Z</t>
   </si>
   <si>
     <t>About Us</t>
@@ -73,7 +73,7 @@
     <t>adventures.report.json</t>
   </si>
   <si>
-    <t>["teaser-columns","cards-magazine"]</t>
+    <t>["teaser-columns","cards-adventures"]</t>
   </si>
   <si>
     <t>adventures</t>
@@ -82,7 +82,7 @@
     <t>wknd-adventures</t>
   </si>
   <si>
-    <t>2026-08-07T07:38:25.541Z</t>
+    <t>2026-08-11T06:35:24.757Z</t>
   </si>
   <si>
     <t>Adventures</t>
@@ -145,7 +145,7 @@
     <t>wknd-faqs</t>
   </si>
   <si>
-    <t>2026-08-07T09:09:22.340Z</t>
+    <t>2026-08-11T06:03:25.152Z</t>
   </si>
   <si>
     <t>FAQs</t>
@@ -163,7 +163,7 @@
     <t>wknd-footer</t>
   </si>
   <si>
-    <t>2026-08-10T10:18:15.420Z</t>
+    <t>2026-08-12T11:10:55.259Z</t>
   </si>
   <si>
     <t>Footer</t>
@@ -184,7 +184,7 @@
     <t>wknd-home</t>
   </si>
   <si>
-    <t>2026-08-07T07:38:53.844Z</t>
+    <t>2026-08-11T06:06:15.138Z</t>
   </si>
   <si>
     <t>WKND Adventures and Travel</t>
@@ -196,7 +196,7 @@
     <t>magazine</t>
   </si>
   <si>
-    <t>2026-08-07T07:38:58.174Z</t>
+    <t>2026-08-11T06:22:12.226Z</t>
   </si>
   <si>
     <t>nav.report.json</t>
@@ -208,7 +208,7 @@
     <t>wknd-nav</t>
   </si>
   <si>
-    <t>2026-08-10T10:18:20.500Z</t>
+    <t>2026-08-12T11:10:49.807Z</t>
   </si>
   <si>
     <t>Nav</t>
@@ -511,7 +511,7 @@
     <t>magazine/arctic-surfing</t>
   </si>
   <si>
-    <t>2026-08-07T09:09:26.685Z</t>
+    <t>2026-08-11T06:19:20.905Z</t>
   </si>
   <si>
     <t>magazine/guide-la-skateparks.report.json</t>
@@ -520,7 +520,7 @@
     <t>magazine/guide-la-skateparks</t>
   </si>
   <si>
-    <t>2026-08-07T09:09:31.643Z</t>
+    <t>2026-08-11T06:19:26.676Z</t>
   </si>
   <si>
     <t>Ultimate Guide to LA Skateparks</t>
@@ -535,7 +535,7 @@
     <t>magazine/san-diego-surf</t>
   </si>
   <si>
-    <t>2026-08-07T09:09:35.685Z</t>
+    <t>2026-08-11T06:19:33.009Z</t>
   </si>
   <si>
     <t>San Diego Surf Spots</t>
@@ -550,7 +550,7 @@
     <t>magazine/ski-touring</t>
   </si>
   <si>
-    <t>2026-08-07T09:09:39.945Z</t>
+    <t>2026-08-11T06:19:38.359Z</t>
   </si>
   <si>
     <t>Ski Touring</t>
@@ -565,13 +565,202 @@
     <t>magazine/western-australia</t>
   </si>
   <si>
-    <t>2026-08-07T09:09:44.331Z</t>
+    <t>2026-08-11T06:19:43.878Z</t>
   </si>
   <si>
     <t>Western Australia</t>
   </si>
   <si>
     <t>https://wknd.site/us/en/magazine/western-australia.html</t>
+  </si>
+  <si>
+    <t>us/en.report.json</t>
+  </si>
+  <si>
+    <t>us/en</t>
+  </si>
+  <si>
+    <t>2026-08-12T11:10:23.761Z</t>
+  </si>
+  <si>
+    <t>us/en/about-us.report.json</t>
+  </si>
+  <si>
+    <t>us/en/about-us</t>
+  </si>
+  <si>
+    <t>2026-08-12T11:10:28.532Z</t>
+  </si>
+  <si>
+    <t>us/en/adventures.report.json</t>
+  </si>
+  <si>
+    <t>us/en/adventures</t>
+  </si>
+  <si>
+    <t>2026-08-12T11:10:44.946Z</t>
+  </si>
+  <si>
+    <t>us/en/faqs.report.json</t>
+  </si>
+  <si>
+    <t>us/en/faqs</t>
+  </si>
+  <si>
+    <t>2026-08-12T11:10:39.124Z</t>
+  </si>
+  <si>
+    <t>us/en/magazine.report.json</t>
+  </si>
+  <si>
+    <t>us/en/magazine</t>
+  </si>
+  <si>
+    <t>2026-08-12T11:10:33.825Z</t>
+  </si>
+  <si>
+    <t>us/en/search.report.json</t>
+  </si>
+  <si>
+    <t>us/en/search</t>
+  </si>
+  <si>
+    <t>2026-08-12T11:11:00.753Z</t>
+  </si>
+  <si>
+    <t>us/en/adventures/bali-surf-camp.report.json</t>
+  </si>
+  <si>
+    <t>us/en/adventures/bali-surf-camp</t>
+  </si>
+  <si>
+    <t>2026-08-12T11:13:39.792Z</t>
+  </si>
+  <si>
+    <t>us/en/adventures/beervana-portland.report.json</t>
+  </si>
+  <si>
+    <t>us/en/adventures/beervana-portland</t>
+  </si>
+  <si>
+    <t>2026-08-12T11:13:44.785Z</t>
+  </si>
+  <si>
+    <t>us/en/adventures/climbing-new-zealand.report.json</t>
+  </si>
+  <si>
+    <t>us/en/adventures/climbing-new-zealand</t>
+  </si>
+  <si>
+    <t>2026-08-12T11:13:50.857Z</t>
+  </si>
+  <si>
+    <t>us/en/adventures/colorado-rock-climbing.report.json</t>
+  </si>
+  <si>
+    <t>us/en/adventures/colorado-rock-climbing</t>
+  </si>
+  <si>
+    <t>2026-08-12T11:13:56.233Z</t>
+  </si>
+  <si>
+    <t>us/en/adventures/cycling-southern-utah.report.json</t>
+  </si>
+  <si>
+    <t>us/en/adventures/cycling-southern-utah</t>
+  </si>
+  <si>
+    <t>2026-08-12T11:14:01.771Z</t>
+  </si>
+  <si>
+    <t>us/en/adventures/cycling-tuscany.report.json</t>
+  </si>
+  <si>
+    <t>us/en/adventures/cycling-tuscany</t>
+  </si>
+  <si>
+    <t>2026-08-12T11:14:08.370Z</t>
+  </si>
+  <si>
+    <t>us/en/adventures/downhill-skiing-wyoming.report.json</t>
+  </si>
+  <si>
+    <t>us/en/adventures/downhill-skiing-wyoming</t>
+  </si>
+  <si>
+    <t>2026-08-12T11:14:14.332Z</t>
+  </si>
+  <si>
+    <t>us/en/adventures/gastronomic-marais-tour.report.json</t>
+  </si>
+  <si>
+    <t>us/en/adventures/gastronomic-marais-tour</t>
+  </si>
+  <si>
+    <t>2026-08-12T11:14:20.890Z</t>
+  </si>
+  <si>
+    <t>us/en/adventures/napa-wine-tasting.report.json</t>
+  </si>
+  <si>
+    <t>us/en/adventures/napa-wine-tasting</t>
+  </si>
+  <si>
+    <t>2026-08-12T11:14:27.665Z</t>
+  </si>
+  <si>
+    <t>us/en/adventures/riverside-camping-australia.report.json</t>
+  </si>
+  <si>
+    <t>us/en/adventures/riverside-camping-australia</t>
+  </si>
+  <si>
+    <t>2026-08-12T11:14:32.303Z</t>
+  </si>
+  <si>
+    <t>us/en/adventures/ski-touring-mont-blanc.report.json</t>
+  </si>
+  <si>
+    <t>us/en/adventures/ski-touring-mont-blanc</t>
+  </si>
+  <si>
+    <t>2026-08-12T11:14:36.207Z</t>
+  </si>
+  <si>
+    <t>us/en/adventures/surf-camp-costa-rica.report.json</t>
+  </si>
+  <si>
+    <t>us/en/adventures/surf-camp-costa-rica</t>
+  </si>
+  <si>
+    <t>2026-08-12T11:14:40.687Z</t>
+  </si>
+  <si>
+    <t>us/en/adventures/tahoe-skiing.report.json</t>
+  </si>
+  <si>
+    <t>us/en/adventures/tahoe-skiing</t>
+  </si>
+  <si>
+    <t>2026-08-12T11:14:47.245Z</t>
+  </si>
+  <si>
+    <t>us/en/adventures/west-coast-cycling.report.json</t>
+  </si>
+  <si>
+    <t>us/en/adventures/west-coast-cycling</t>
+  </si>
+  <si>
+    <t>2026-08-12T11:14:52.150Z</t>
+  </si>
+  <si>
+    <t>us/en/adventures/whistler-mountain-biking.report.json</t>
+  </si>
+  <si>
+    <t>us/en/adventures/whistler-mountain-biking</t>
+  </si>
+  <si>
+    <t>2026-08-12T11:14:57.767Z</t>
   </si>
   <si>
     <t>us/en/adventures/yosemite-backpacking.html.report.json</t>
@@ -592,6 +781,60 @@
   </si>
   <si>
     <t>2026-08-10T09:12:25.649Z</t>
+  </si>
+  <si>
+    <t>us/en/adventures/yosemite-backpacking.report.json</t>
+  </si>
+  <si>
+    <t>us/en/adventures/yosemite-backpacking</t>
+  </si>
+  <si>
+    <t>2026-08-12T11:15:01.781Z</t>
+  </si>
+  <si>
+    <t>us/en/magazine/arctic-surfing.report.json</t>
+  </si>
+  <si>
+    <t>us/en/magazine/arctic-surfing</t>
+  </si>
+  <si>
+    <t>2026-08-12T11:13:13.925Z</t>
+  </si>
+  <si>
+    <t>us/en/magazine/guide-la-skateparks.report.json</t>
+  </si>
+  <si>
+    <t>us/en/magazine/guide-la-skateparks</t>
+  </si>
+  <si>
+    <t>2026-08-12T11:13:18.992Z</t>
+  </si>
+  <si>
+    <t>us/en/magazine/san-diego-surf.report.json</t>
+  </si>
+  <si>
+    <t>us/en/magazine/san-diego-surf</t>
+  </si>
+  <si>
+    <t>2026-08-12T11:13:25.163Z</t>
+  </si>
+  <si>
+    <t>us/en/magazine/ski-touring.report.json</t>
+  </si>
+  <si>
+    <t>us/en/magazine/ski-touring</t>
+  </si>
+  <si>
+    <t>2026-08-12T11:13:30.153Z</t>
+  </si>
+  <si>
+    <t>us/en/magazine/western-australia.report.json</t>
+  </si>
+  <si>
+    <t>us/en/magazine/western-australia</t>
+  </si>
+  <si>
+    <t>2026-08-12T11:13:35.310Z</t>
   </si>
 </sst>
 </file>
@@ -980,11 +1223,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J62"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="4" width="50" customWidth="1"/>
-    <col min="5" max="5" width="44" customWidth="1"/>
+    <col min="5" max="5" width="46" customWidth="1"/>
     <col min="7" max="7" width="17" customWidth="1"/>
     <col min="8" max="8" width="26" customWidth="1"/>
     <col min="9" max="10" width="50" customWidth="1"/>
@@ -2083,31 +2326,895 @@
         <v>187</v>
       </c>
       <c r="B35" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="C35" t="s">
+        <v>12</v>
+      </c>
+      <c r="D35" t="s">
+        <v>12</v>
+      </c>
+      <c r="E35" t="s">
         <v>188</v>
       </c>
-      <c r="D35" t="s">
+      <c r="F35" t="s">
+        <v>14</v>
+      </c>
+      <c r="G35" t="s">
+        <v>56</v>
+      </c>
+      <c r="H35" t="s">
         <v>189</v>
       </c>
-      <c r="E35" t="s">
+      <c r="I35" t="s">
+        <v>58</v>
+      </c>
+      <c r="J35" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>190</v>
       </c>
-      <c r="F35" t="s">
+      <c r="B36" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" t="s">
+        <v>12</v>
+      </c>
+      <c r="D36" t="s">
+        <v>12</v>
+      </c>
+      <c r="E36" t="s">
         <v>191</v>
       </c>
-      <c r="G35" t="s">
-        <v>12</v>
-      </c>
-      <c r="H35" t="s">
+      <c r="F36" t="s">
+        <v>14</v>
+      </c>
+      <c r="G36" t="s">
+        <v>15</v>
+      </c>
+      <c r="H36" t="s">
         <v>192</v>
       </c>
-      <c r="I35" t="s">
-        <v>12</v>
-      </c>
-      <c r="J35" t="s">
+      <c r="I36" t="s">
+        <v>17</v>
+      </c>
+      <c r="J36" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>193</v>
+      </c>
+      <c r="B37" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" t="s">
+        <v>12</v>
+      </c>
+      <c r="D37" t="s">
+        <v>12</v>
+      </c>
+      <c r="E37" t="s">
+        <v>194</v>
+      </c>
+      <c r="F37" t="s">
+        <v>14</v>
+      </c>
+      <c r="G37" t="s">
+        <v>22</v>
+      </c>
+      <c r="H37" t="s">
+        <v>195</v>
+      </c>
+      <c r="I37" t="s">
+        <v>24</v>
+      </c>
+      <c r="J37" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>196</v>
+      </c>
+      <c r="B38" t="s">
+        <v>41</v>
+      </c>
+      <c r="C38" t="s">
+        <v>12</v>
+      </c>
+      <c r="D38" t="s">
+        <v>12</v>
+      </c>
+      <c r="E38" t="s">
+        <v>197</v>
+      </c>
+      <c r="F38" t="s">
+        <v>14</v>
+      </c>
+      <c r="G38" t="s">
+        <v>43</v>
+      </c>
+      <c r="H38" t="s">
+        <v>198</v>
+      </c>
+      <c r="I38" t="s">
+        <v>45</v>
+      </c>
+      <c r="J38" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>199</v>
+      </c>
+      <c r="B39" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" t="s">
+        <v>12</v>
+      </c>
+      <c r="D39" t="s">
+        <v>12</v>
+      </c>
+      <c r="E39" t="s">
+        <v>200</v>
+      </c>
+      <c r="F39" t="s">
+        <v>14</v>
+      </c>
+      <c r="G39" t="s">
+        <v>36</v>
+      </c>
+      <c r="H39" t="s">
+        <v>201</v>
+      </c>
+      <c r="I39" t="s">
+        <v>38</v>
+      </c>
+      <c r="J39" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>202</v>
+      </c>
+      <c r="B40" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40" t="s">
+        <v>12</v>
+      </c>
+      <c r="D40" t="s">
+        <v>12</v>
+      </c>
+      <c r="E40" t="s">
+        <v>203</v>
+      </c>
+      <c r="F40" t="s">
+        <v>14</v>
+      </c>
+      <c r="G40" t="s">
+        <v>69</v>
+      </c>
+      <c r="H40" t="s">
+        <v>204</v>
+      </c>
+      <c r="I40" t="s">
+        <v>71</v>
+      </c>
+      <c r="J40" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>205</v>
+      </c>
+      <c r="B41" t="s">
+        <v>73</v>
+      </c>
+      <c r="C41" t="s">
+        <v>12</v>
+      </c>
+      <c r="D41" t="s">
+        <v>12</v>
+      </c>
+      <c r="E41" t="s">
+        <v>206</v>
+      </c>
+      <c r="F41" t="s">
+        <v>14</v>
+      </c>
+      <c r="G41" t="s">
+        <v>75</v>
+      </c>
+      <c r="H41" t="s">
+        <v>207</v>
+      </c>
+      <c r="I41" t="s">
+        <v>77</v>
+      </c>
+      <c r="J41" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>208</v>
+      </c>
+      <c r="B42" t="s">
+        <v>73</v>
+      </c>
+      <c r="C42" t="s">
+        <v>12</v>
+      </c>
+      <c r="D42" t="s">
+        <v>12</v>
+      </c>
+      <c r="E42" t="s">
+        <v>209</v>
+      </c>
+      <c r="F42" t="s">
+        <v>14</v>
+      </c>
+      <c r="G42" t="s">
+        <v>75</v>
+      </c>
+      <c r="H42" t="s">
+        <v>210</v>
+      </c>
+      <c r="I42" t="s">
+        <v>82</v>
+      </c>
+      <c r="J42" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>211</v>
+      </c>
+      <c r="B43" t="s">
+        <v>73</v>
+      </c>
+      <c r="C43" t="s">
+        <v>12</v>
+      </c>
+      <c r="D43" t="s">
+        <v>12</v>
+      </c>
+      <c r="E43" t="s">
+        <v>212</v>
+      </c>
+      <c r="F43" t="s">
+        <v>14</v>
+      </c>
+      <c r="G43" t="s">
+        <v>75</v>
+      </c>
+      <c r="H43" t="s">
+        <v>213</v>
+      </c>
+      <c r="I43" t="s">
+        <v>87</v>
+      </c>
+      <c r="J43" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>214</v>
+      </c>
+      <c r="B44" t="s">
+        <v>73</v>
+      </c>
+      <c r="C44" t="s">
+        <v>12</v>
+      </c>
+      <c r="D44" t="s">
+        <v>12</v>
+      </c>
+      <c r="E44" t="s">
+        <v>215</v>
+      </c>
+      <c r="F44" t="s">
+        <v>14</v>
+      </c>
+      <c r="G44" t="s">
+        <v>75</v>
+      </c>
+      <c r="H44" t="s">
+        <v>216</v>
+      </c>
+      <c r="I44" t="s">
+        <v>92</v>
+      </c>
+      <c r="J44" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>217</v>
+      </c>
+      <c r="B45" t="s">
+        <v>73</v>
+      </c>
+      <c r="C45" t="s">
+        <v>12</v>
+      </c>
+      <c r="D45" t="s">
+        <v>12</v>
+      </c>
+      <c r="E45" t="s">
+        <v>218</v>
+      </c>
+      <c r="F45" t="s">
+        <v>14</v>
+      </c>
+      <c r="G45" t="s">
+        <v>75</v>
+      </c>
+      <c r="H45" t="s">
+        <v>219</v>
+      </c>
+      <c r="I45" t="s">
+        <v>97</v>
+      </c>
+      <c r="J45" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>220</v>
+      </c>
+      <c r="B46" t="s">
+        <v>73</v>
+      </c>
+      <c r="C46" t="s">
+        <v>12</v>
+      </c>
+      <c r="D46" t="s">
+        <v>12</v>
+      </c>
+      <c r="E46" t="s">
+        <v>221</v>
+      </c>
+      <c r="F46" t="s">
+        <v>14</v>
+      </c>
+      <c r="G46" t="s">
+        <v>75</v>
+      </c>
+      <c r="H46" t="s">
+        <v>222</v>
+      </c>
+      <c r="I46" t="s">
+        <v>102</v>
+      </c>
+      <c r="J46" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>223</v>
+      </c>
+      <c r="B47" t="s">
+        <v>73</v>
+      </c>
+      <c r="C47" t="s">
+        <v>12</v>
+      </c>
+      <c r="D47" t="s">
+        <v>12</v>
+      </c>
+      <c r="E47" t="s">
+        <v>224</v>
+      </c>
+      <c r="F47" t="s">
+        <v>14</v>
+      </c>
+      <c r="G47" t="s">
+        <v>75</v>
+      </c>
+      <c r="H47" t="s">
+        <v>225</v>
+      </c>
+      <c r="I47" t="s">
+        <v>107</v>
+      </c>
+      <c r="J47" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>226</v>
+      </c>
+      <c r="B48" t="s">
+        <v>73</v>
+      </c>
+      <c r="C48" t="s">
+        <v>12</v>
+      </c>
+      <c r="D48" t="s">
+        <v>12</v>
+      </c>
+      <c r="E48" t="s">
+        <v>227</v>
+      </c>
+      <c r="F48" t="s">
+        <v>14</v>
+      </c>
+      <c r="G48" t="s">
+        <v>75</v>
+      </c>
+      <c r="H48" t="s">
+        <v>228</v>
+      </c>
+      <c r="I48" t="s">
+        <v>112</v>
+      </c>
+      <c r="J48" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>229</v>
+      </c>
+      <c r="B49" t="s">
+        <v>73</v>
+      </c>
+      <c r="C49" t="s">
+        <v>12</v>
+      </c>
+      <c r="D49" t="s">
+        <v>12</v>
+      </c>
+      <c r="E49" t="s">
+        <v>230</v>
+      </c>
+      <c r="F49" t="s">
+        <v>14</v>
+      </c>
+      <c r="G49" t="s">
+        <v>75</v>
+      </c>
+      <c r="H49" t="s">
+        <v>231</v>
+      </c>
+      <c r="I49" t="s">
+        <v>117</v>
+      </c>
+      <c r="J49" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>232</v>
+      </c>
+      <c r="B50" t="s">
+        <v>73</v>
+      </c>
+      <c r="C50" t="s">
+        <v>12</v>
+      </c>
+      <c r="D50" t="s">
+        <v>12</v>
+      </c>
+      <c r="E50" t="s">
+        <v>233</v>
+      </c>
+      <c r="F50" t="s">
+        <v>14</v>
+      </c>
+      <c r="G50" t="s">
+        <v>75</v>
+      </c>
+      <c r="H50" t="s">
+        <v>234</v>
+      </c>
+      <c r="I50" t="s">
+        <v>122</v>
+      </c>
+      <c r="J50" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>235</v>
+      </c>
+      <c r="B51" t="s">
+        <v>73</v>
+      </c>
+      <c r="C51" t="s">
+        <v>12</v>
+      </c>
+      <c r="D51" t="s">
+        <v>12</v>
+      </c>
+      <c r="E51" t="s">
+        <v>236</v>
+      </c>
+      <c r="F51" t="s">
+        <v>14</v>
+      </c>
+      <c r="G51" t="s">
+        <v>75</v>
+      </c>
+      <c r="H51" t="s">
+        <v>237</v>
+      </c>
+      <c r="I51" t="s">
+        <v>127</v>
+      </c>
+      <c r="J51" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>238</v>
+      </c>
+      <c r="B52" t="s">
+        <v>73</v>
+      </c>
+      <c r="C52" t="s">
+        <v>12</v>
+      </c>
+      <c r="D52" t="s">
+        <v>12</v>
+      </c>
+      <c r="E52" t="s">
+        <v>239</v>
+      </c>
+      <c r="F52" t="s">
+        <v>14</v>
+      </c>
+      <c r="G52" t="s">
+        <v>75</v>
+      </c>
+      <c r="H52" t="s">
+        <v>240</v>
+      </c>
+      <c r="I52" t="s">
+        <v>132</v>
+      </c>
+      <c r="J52" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>241</v>
+      </c>
+      <c r="B53" t="s">
+        <v>73</v>
+      </c>
+      <c r="C53" t="s">
+        <v>12</v>
+      </c>
+      <c r="D53" t="s">
+        <v>12</v>
+      </c>
+      <c r="E53" t="s">
+        <v>242</v>
+      </c>
+      <c r="F53" t="s">
+        <v>14</v>
+      </c>
+      <c r="G53" t="s">
+        <v>75</v>
+      </c>
+      <c r="H53" t="s">
+        <v>243</v>
+      </c>
+      <c r="I53" t="s">
+        <v>137</v>
+      </c>
+      <c r="J53" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>244</v>
+      </c>
+      <c r="B54" t="s">
+        <v>73</v>
+      </c>
+      <c r="C54" t="s">
+        <v>12</v>
+      </c>
+      <c r="D54" t="s">
+        <v>12</v>
+      </c>
+      <c r="E54" t="s">
+        <v>245</v>
+      </c>
+      <c r="F54" t="s">
+        <v>14</v>
+      </c>
+      <c r="G54" t="s">
+        <v>75</v>
+      </c>
+      <c r="H54" t="s">
+        <v>246</v>
+      </c>
+      <c r="I54" t="s">
+        <v>142</v>
+      </c>
+      <c r="J54" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>247</v>
+      </c>
+      <c r="B55" t="s">
+        <v>73</v>
+      </c>
+      <c r="C55" t="s">
+        <v>12</v>
+      </c>
+      <c r="D55" t="s">
+        <v>12</v>
+      </c>
+      <c r="E55" t="s">
+        <v>248</v>
+      </c>
+      <c r="F55" t="s">
+        <v>14</v>
+      </c>
+      <c r="G55" t="s">
+        <v>75</v>
+      </c>
+      <c r="H55" t="s">
+        <v>249</v>
+      </c>
+      <c r="I55" t="s">
+        <v>147</v>
+      </c>
+      <c r="J55" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>250</v>
+      </c>
+      <c r="B56" t="s">
+        <v>12</v>
+      </c>
+      <c r="C56" t="s">
+        <v>251</v>
+      </c>
+      <c r="D56" t="s">
+        <v>252</v>
+      </c>
+      <c r="E56" t="s">
+        <v>253</v>
+      </c>
+      <c r="F56" t="s">
+        <v>254</v>
+      </c>
+      <c r="G56" t="s">
+        <v>12</v>
+      </c>
+      <c r="H56" t="s">
+        <v>255</v>
+      </c>
+      <c r="I56" t="s">
+        <v>12</v>
+      </c>
+      <c r="J56" t="s">
         <v>153</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>256</v>
+      </c>
+      <c r="B57" t="s">
+        <v>73</v>
+      </c>
+      <c r="C57" t="s">
+        <v>12</v>
+      </c>
+      <c r="D57" t="s">
+        <v>12</v>
+      </c>
+      <c r="E57" t="s">
+        <v>257</v>
+      </c>
+      <c r="F57" t="s">
+        <v>14</v>
+      </c>
+      <c r="G57" t="s">
+        <v>75</v>
+      </c>
+      <c r="H57" t="s">
+        <v>258</v>
+      </c>
+      <c r="I57" t="s">
+        <v>152</v>
+      </c>
+      <c r="J57" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>259</v>
+      </c>
+      <c r="B58" t="s">
+        <v>27</v>
+      </c>
+      <c r="C58" t="s">
+        <v>12</v>
+      </c>
+      <c r="D58" t="s">
+        <v>12</v>
+      </c>
+      <c r="E58" t="s">
+        <v>260</v>
+      </c>
+      <c r="F58" t="s">
+        <v>14</v>
+      </c>
+      <c r="G58" t="s">
+        <v>29</v>
+      </c>
+      <c r="H58" t="s">
+        <v>261</v>
+      </c>
+      <c r="I58" t="s">
+        <v>31</v>
+      </c>
+      <c r="J58" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>262</v>
+      </c>
+      <c r="B59" t="s">
+        <v>27</v>
+      </c>
+      <c r="C59" t="s">
+        <v>12</v>
+      </c>
+      <c r="D59" t="s">
+        <v>12</v>
+      </c>
+      <c r="E59" t="s">
+        <v>263</v>
+      </c>
+      <c r="F59" t="s">
+        <v>14</v>
+      </c>
+      <c r="G59" t="s">
+        <v>29</v>
+      </c>
+      <c r="H59" t="s">
+        <v>264</v>
+      </c>
+      <c r="I59" t="s">
+        <v>170</v>
+      </c>
+      <c r="J59" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>265</v>
+      </c>
+      <c r="B60" t="s">
+        <v>27</v>
+      </c>
+      <c r="C60" t="s">
+        <v>12</v>
+      </c>
+      <c r="D60" t="s">
+        <v>12</v>
+      </c>
+      <c r="E60" t="s">
+        <v>266</v>
+      </c>
+      <c r="F60" t="s">
+        <v>14</v>
+      </c>
+      <c r="G60" t="s">
+        <v>29</v>
+      </c>
+      <c r="H60" t="s">
+        <v>267</v>
+      </c>
+      <c r="I60" t="s">
+        <v>175</v>
+      </c>
+      <c r="J60" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>268</v>
+      </c>
+      <c r="B61" t="s">
+        <v>27</v>
+      </c>
+      <c r="C61" t="s">
+        <v>12</v>
+      </c>
+      <c r="D61" t="s">
+        <v>12</v>
+      </c>
+      <c r="E61" t="s">
+        <v>269</v>
+      </c>
+      <c r="F61" t="s">
+        <v>14</v>
+      </c>
+      <c r="G61" t="s">
+        <v>29</v>
+      </c>
+      <c r="H61" t="s">
+        <v>270</v>
+      </c>
+      <c r="I61" t="s">
+        <v>180</v>
+      </c>
+      <c r="J61" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>271</v>
+      </c>
+      <c r="B62" t="s">
+        <v>27</v>
+      </c>
+      <c r="C62" t="s">
+        <v>12</v>
+      </c>
+      <c r="D62" t="s">
+        <v>12</v>
+      </c>
+      <c r="E62" t="s">
+        <v>272</v>
+      </c>
+      <c r="F62" t="s">
+        <v>14</v>
+      </c>
+      <c r="G62" t="s">
+        <v>29</v>
+      </c>
+      <c r="H62" t="s">
+        <v>273</v>
+      </c>
+      <c r="I62" t="s">
+        <v>185</v>
+      </c>
+      <c r="J62" t="s">
+        <v>186</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-wknd-adventure.report.xlsx
+++ b/tools/importer/reports/import-wknd-adventure.report.xlsx
@@ -607,7 +607,7 @@
     <t>us/en/faqs</t>
   </si>
   <si>
-    <t>2026-08-12T11:10:39.124Z</t>
+    <t>2026-08-12T11:51:45.004Z</t>
   </si>
   <si>
     <t>us/en/magazine.report.json</t>
@@ -634,7 +634,7 @@
     <t>us/en/adventures/bali-surf-camp</t>
   </si>
   <si>
-    <t>2026-08-12T11:13:39.792Z</t>
+    <t>2026-08-13T13:56:20.947Z</t>
   </si>
   <si>
     <t>us/en/adventures/beervana-portland.report.json</t>
@@ -643,7 +643,7 @@
     <t>us/en/adventures/beervana-portland</t>
   </si>
   <si>
-    <t>2026-08-12T11:13:44.785Z</t>
+    <t>2026-08-13T13:56:25.208Z</t>
   </si>
   <si>
     <t>us/en/adventures/climbing-new-zealand.report.json</t>
@@ -652,7 +652,7 @@
     <t>us/en/adventures/climbing-new-zealand</t>
   </si>
   <si>
-    <t>2026-08-12T11:13:50.857Z</t>
+    <t>2026-08-13T13:56:30.144Z</t>
   </si>
   <si>
     <t>us/en/adventures/colorado-rock-climbing.report.json</t>
@@ -661,7 +661,7 @@
     <t>us/en/adventures/colorado-rock-climbing</t>
   </si>
   <si>
-    <t>2026-08-12T11:13:56.233Z</t>
+    <t>2026-08-13T13:56:34.346Z</t>
   </si>
   <si>
     <t>us/en/adventures/cycling-southern-utah.report.json</t>
@@ -670,7 +670,7 @@
     <t>us/en/adventures/cycling-southern-utah</t>
   </si>
   <si>
-    <t>2026-08-12T11:14:01.771Z</t>
+    <t>2026-08-13T13:56:39.594Z</t>
   </si>
   <si>
     <t>us/en/adventures/cycling-tuscany.report.json</t>
@@ -679,7 +679,7 @@
     <t>us/en/adventures/cycling-tuscany</t>
   </si>
   <si>
-    <t>2026-08-12T11:14:08.370Z</t>
+    <t>2026-08-13T13:56:44.710Z</t>
   </si>
   <si>
     <t>us/en/adventures/downhill-skiing-wyoming.report.json</t>
@@ -688,7 +688,7 @@
     <t>us/en/adventures/downhill-skiing-wyoming</t>
   </si>
   <si>
-    <t>2026-08-12T11:14:14.332Z</t>
+    <t>2026-08-13T13:56:49.961Z</t>
   </si>
   <si>
     <t>us/en/adventures/gastronomic-marais-tour.report.json</t>
@@ -697,7 +697,7 @@
     <t>us/en/adventures/gastronomic-marais-tour</t>
   </si>
   <si>
-    <t>2026-08-12T11:14:20.890Z</t>
+    <t>2026-08-13T13:56:55.269Z</t>
   </si>
   <si>
     <t>us/en/adventures/napa-wine-tasting.report.json</t>
@@ -706,7 +706,7 @@
     <t>us/en/adventures/napa-wine-tasting</t>
   </si>
   <si>
-    <t>2026-08-12T11:14:27.665Z</t>
+    <t>2026-08-13T13:56:59.952Z</t>
   </si>
   <si>
     <t>us/en/adventures/riverside-camping-australia.report.json</t>
@@ -715,7 +715,7 @@
     <t>us/en/adventures/riverside-camping-australia</t>
   </si>
   <si>
-    <t>2026-08-12T11:14:32.303Z</t>
+    <t>2026-08-13T13:57:04.923Z</t>
   </si>
   <si>
     <t>us/en/adventures/ski-touring-mont-blanc.report.json</t>
@@ -724,7 +724,7 @@
     <t>us/en/adventures/ski-touring-mont-blanc</t>
   </si>
   <si>
-    <t>2026-08-12T11:14:36.207Z</t>
+    <t>2026-08-13T13:57:08.893Z</t>
   </si>
   <si>
     <t>us/en/adventures/surf-camp-costa-rica.report.json</t>
@@ -733,7 +733,7 @@
     <t>us/en/adventures/surf-camp-costa-rica</t>
   </si>
   <si>
-    <t>2026-08-12T11:14:40.687Z</t>
+    <t>2026-08-13T13:57:13.664Z</t>
   </si>
   <si>
     <t>us/en/adventures/tahoe-skiing.report.json</t>
@@ -742,7 +742,7 @@
     <t>us/en/adventures/tahoe-skiing</t>
   </si>
   <si>
-    <t>2026-08-12T11:14:47.245Z</t>
+    <t>2026-08-13T13:57:19.872Z</t>
   </si>
   <si>
     <t>us/en/adventures/west-coast-cycling.report.json</t>
@@ -751,7 +751,7 @@
     <t>us/en/adventures/west-coast-cycling</t>
   </si>
   <si>
-    <t>2026-08-12T11:14:52.150Z</t>
+    <t>2026-08-13T13:57:25.480Z</t>
   </si>
   <si>
     <t>us/en/adventures/whistler-mountain-biking.report.json</t>
@@ -760,7 +760,7 @@
     <t>us/en/adventures/whistler-mountain-biking</t>
   </si>
   <si>
-    <t>2026-08-12T11:14:57.767Z</t>
+    <t>2026-08-13T13:57:30.131Z</t>
   </si>
   <si>
     <t>us/en/adventures/yosemite-backpacking.html.report.json</t>
@@ -789,7 +789,7 @@
     <t>us/en/adventures/yosemite-backpacking</t>
   </si>
   <si>
-    <t>2026-08-12T11:15:01.781Z</t>
+    <t>2026-08-13T13:57:34.057Z</t>
   </si>
   <si>
     <t>us/en/magazine/arctic-surfing.report.json</t>
@@ -798,7 +798,7 @@
     <t>us/en/magazine/arctic-surfing</t>
   </si>
   <si>
-    <t>2026-08-12T11:13:13.925Z</t>
+    <t>2026-08-12T12:45:50.848Z</t>
   </si>
   <si>
     <t>us/en/magazine/guide-la-skateparks.report.json</t>
@@ -807,7 +807,7 @@
     <t>us/en/magazine/guide-la-skateparks</t>
   </si>
   <si>
-    <t>2026-08-12T11:13:18.992Z</t>
+    <t>2026-08-12T12:45:56.055Z</t>
   </si>
   <si>
     <t>us/en/magazine/san-diego-surf.report.json</t>
@@ -816,7 +816,7 @@
     <t>us/en/magazine/san-diego-surf</t>
   </si>
   <si>
-    <t>2026-08-12T11:13:25.163Z</t>
+    <t>2026-08-12T12:46:00.979Z</t>
   </si>
   <si>
     <t>us/en/magazine/ski-touring.report.json</t>
@@ -825,7 +825,7 @@
     <t>us/en/magazine/ski-touring</t>
   </si>
   <si>
-    <t>2026-08-12T11:13:30.153Z</t>
+    <t>2026-08-12T12:46:07.398Z</t>
   </si>
   <si>
     <t>us/en/magazine/western-australia.report.json</t>
@@ -834,7 +834,7 @@
     <t>us/en/magazine/western-australia</t>
   </si>
   <si>
-    <t>2026-08-12T11:13:35.310Z</t>
+    <t>2026-08-12T12:46:11.910Z</t>
   </si>
 </sst>
 </file>
